--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118743798</v>
+        <v>118743949</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387997</v>
+        <v>388050</v>
       </c>
       <c r="R4" t="n">
-        <v>6611589</v>
+        <v>6611545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,6 +974,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -990,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118743949</v>
+        <v>118743798</v>
       </c>
       <c r="B5" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388050</v>
+        <v>387997</v>
       </c>
       <c r="R5" t="n">
-        <v>6611545</v>
+        <v>6611589</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,26 +1096,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118744173</v>
+        <v>118743468</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388034</v>
+        <v>388016</v>
       </c>
       <c r="R2" t="n">
-        <v>6611517</v>
+        <v>6611534</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118743468</v>
+        <v>118743798</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388016</v>
+        <v>387997</v>
       </c>
       <c r="R3" t="n">
-        <v>6611534</v>
+        <v>6611589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1010,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118743798</v>
+        <v>118744173</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1043,17 +1034,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387997</v>
+        <v>388034</v>
       </c>
       <c r="R5" t="n">
-        <v>6611589</v>
+        <v>6611517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118743468</v>
+        <v>118743949</v>
       </c>
       <c r="B2" t="n">
         <v>79102</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388016</v>
+        <v>388050</v>
       </c>
       <c r="R2" t="n">
-        <v>6611534</v>
+        <v>6611545</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118743798</v>
+        <v>118743468</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387997</v>
+        <v>388016</v>
       </c>
       <c r="R3" t="n">
-        <v>6611589</v>
+        <v>6611534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118743949</v>
+        <v>118744173</v>
       </c>
       <c r="B4" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388050</v>
+        <v>388034</v>
       </c>
       <c r="R4" t="n">
-        <v>6611545</v>
+        <v>6611517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,26 +994,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118744173</v>
+        <v>118743798</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1034,26 +1043,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388034</v>
+        <v>387997</v>
       </c>
       <c r="R5" t="n">
-        <v>6611517</v>
+        <v>6611589</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118743949</v>
+        <v>118744173</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388050</v>
+        <v>388034</v>
       </c>
       <c r="R2" t="n">
-        <v>6611545</v>
+        <v>6611517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118743468</v>
+        <v>118743949</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388016</v>
+        <v>388050</v>
       </c>
       <c r="R3" t="n">
-        <v>6611534</v>
+        <v>6611545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,6 +872,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118744173</v>
+        <v>118743468</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388034</v>
+        <v>388016</v>
       </c>
       <c r="R4" t="n">
-        <v>6611517</v>
+        <v>6611534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         <v>118743798</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118744173</v>
+        <v>118743798</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -708,26 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388034</v>
+        <v>387997</v>
       </c>
       <c r="R2" t="n">
-        <v>6611517</v>
+        <v>6611589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118743949</v>
+        <v>118744173</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388050</v>
+        <v>388034</v>
       </c>
       <c r="R3" t="n">
-        <v>6611545</v>
+        <v>6611517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,26 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1010,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118743798</v>
+        <v>118743949</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>79109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387997</v>
+        <v>388050</v>
       </c>
       <c r="R5" t="n">
-        <v>6611589</v>
+        <v>6611545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,6 +1076,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,26 +1145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R6" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1182,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,17 +1256,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R7" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1145,17 +1145,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R6" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1191,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1223,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1256,26 +1265,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R7" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>121344587</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>121344586</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,26 +1145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R6" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1182,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,17 +1256,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R7" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,17 +1145,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R6" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1191,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1223,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,26 +1265,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R7" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1145,26 +1145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R6" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1182,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1265,17 +1256,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R7" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>121344586</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>121344587</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,17 +1145,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R6" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1191,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1223,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,26 +1265,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R7" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344587</v>
+        <v>121344586</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1145,26 +1145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388034</v>
+        <v>387998</v>
       </c>
       <c r="R6" t="n">
-        <v>6611516</v>
+        <v>6611589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1182,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>S-Arv-0846</t>
+          <t>S-Arv-0847</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344586</v>
+        <v>121344587</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1265,17 +1256,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R7" t="n">
-        <v>6611589</v>
+        <v>6611516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>S-Arv-0847</t>
+          <t>S-Arv-0846</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>121344586</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>121344587</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>122786990</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,6 +1474,442 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125684769</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388040</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6611514</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684879</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388031</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611583</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125684880</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>388034</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611515</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125684770</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>388007</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6611582</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1476,54 +1476,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684769</v>
+        <v>125684880</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388034</v>
       </c>
       <c r="R9" t="n">
-        <v>6611514</v>
+        <v>6611515</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1550,12 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1590,12 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,50 +1680,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684880</v>
+        <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388034</v>
+        <v>388040</v>
       </c>
       <c r="R11" t="n">
-        <v>6611515</v>
+        <v>6611514</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1764,12 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1804,12 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>125684880</v>
       </c>
       <c r="B9" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>125684880</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>125684880</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>125684880</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1680,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684769</v>
+        <v>125684770</v>
       </c>
       <c r="B11" t="n">
         <v>98349</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388040</v>
+        <v>388007</v>
       </c>
       <c r="R11" t="n">
-        <v>6611514</v>
+        <v>6611582</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684770</v>
+        <v>125684769</v>
       </c>
       <c r="B12" t="n">
         <v>98349</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388007</v>
+        <v>388040</v>
       </c>
       <c r="R12" t="n">
-        <v>6611582</v>
+        <v>6611514</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1581,7 +1581,7 @@
         <v>125684879</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684770</v>
+        <v>125684769</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388007</v>
+        <v>388040</v>
       </c>
       <c r="R11" t="n">
-        <v>6611582</v>
+        <v>6611514</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684769</v>
+        <v>125684770</v>
       </c>
       <c r="B12" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388040</v>
+        <v>388007</v>
       </c>
       <c r="R12" t="n">
-        <v>6611514</v>
+        <v>6611582</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1890,238 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127272007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>388012</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6611581</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127272064</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>388011</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6611587</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -1895,7 +1895,7 @@
         <v>127272007</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>127272064</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23084-2024 artfynd.xlsx
+++ b/artfynd/A 23084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118743949</v>
+        <v>118335258</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Glansbergen, Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388050</v>
+        <v>388067</v>
       </c>
       <c r="R2" t="n">
-        <v>6611545</v>
+        <v>6611575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,51 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118743798</v>
+        <v>123475596</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387997</v>
+        <v>387935</v>
       </c>
       <c r="R3" t="n">
-        <v>6611589</v>
+        <v>6611590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,12 +872,7 @@
         <v>118743468</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +900,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1001,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118744173</v>
+        <v>118743949</v>
       </c>
       <c r="B5" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388034</v>
+        <v>388050</v>
       </c>
       <c r="R5" t="n">
-        <v>6611517</v>
+        <v>6611545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,6 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1112,53 +1083,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344586</v>
+        <v>125684880</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Glansbergen, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387998</v>
+        <v>388034</v>
       </c>
       <c r="R6" t="n">
-        <v>6611589</v>
+        <v>6611515</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,19 +1146,19 @@
           <t>Brunskog</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>S-Arv-0847</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,75 +1173,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344587</v>
+        <v>123698850</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388034</v>
+        <v>388084</v>
       </c>
       <c r="R7" t="n">
-        <v>6611516</v>
+        <v>6611518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,19 +1248,14 @@
           <t>Brunskog</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>S-Arv-0846</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,82 +1270,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122786990</v>
+        <v>124451852</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Glansbergen, Brunskog, Vrm, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387990</v>
+        <v>388087</v>
       </c>
       <c r="R8" t="n">
-        <v>6611571</v>
+        <v>6611564</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,27 +1358,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 styck färsk spillning under tall. Inom avverkningsanmäld område.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,60 +1388,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684880</v>
+        <v>118743798</v>
       </c>
       <c r="B9" t="n">
-        <v>79595</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388034</v>
+        <v>387997</v>
       </c>
       <c r="R9" t="n">
-        <v>6611515</v>
+        <v>6611589</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,17 +1465,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,22 +1485,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125684879</v>
+        <v>118744173</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,20 +1525,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388031</v>
+        <v>388034</v>
       </c>
       <c r="R10" t="n">
-        <v>6611583</v>
+        <v>6611517</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,17 +1571,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684769</v>
+        <v>121344586</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,24 +1631,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388040</v>
+        <v>387998</v>
       </c>
       <c r="R11" t="n">
-        <v>6611514</v>
+        <v>6611589</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,19 +1666,19 @@
           <t>Brunskog</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>S-Arv-0847</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,22 +1693,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684770</v>
+        <v>121344587</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,22 +1739,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388007</v>
+        <v>388034</v>
       </c>
       <c r="R12" t="n">
-        <v>6611582</v>
+        <v>6611516</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,19 +1781,19 @@
           <t>Brunskog</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>S-Arv-0846</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1808,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127272007</v>
+        <v>125684769</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,27 +1854,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388012</v>
+        <v>388040</v>
       </c>
       <c r="R13" t="n">
-        <v>6611581</v>
+        <v>6611514</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,22 +1893,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,22 +1918,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127272064</v>
+        <v>125684770</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,27 +1960,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388011</v>
+        <v>388007</v>
       </c>
       <c r="R14" t="n">
-        <v>6611587</v>
+        <v>6611582</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,22 +1999,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,15 +2024,451 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125684868</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>388005</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6611515</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125684879</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>388031</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6611583</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127272007</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>388012</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6611581</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Sofia Martinell-Funch</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Sofia Martinell-Funch</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127272064</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>388011</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6611587</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
